--- a/4_VERIFICATION_VALIDATION/Validation-Test-Cases.xlsx
+++ b/4_VERIFICATION_VALIDATION/Validation-Test-Cases.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -442,62 +442,46 @@
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Validation Test Cases - Smart Home Security System</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>IEEE 29148:2018 | Phase 4 Verification &amp; Validation</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Test ID</t>
+          <t>Test Case Name</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Test Name</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Precondition</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Expected Outcomes</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Related Requirements</t>
         </is>
@@ -506,1458 +490,1317 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VAL-001</t>
+          <t>VAL-001: User Onboarding - Setup Wizard</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>User Onboarding - Setup Wizard</t>
+          <t>Verify new user can complete setup &lt;30 min</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Verify new user can complete setup &lt;30 min</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>First-time homeowner sets up system | Fresh Raspberry Pi 4B, sensors in boxes, user with no technical background</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>First-time homeowner sets up system | Fresh Raspberry Pi 4B, sensors in boxes, user with no technical background</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Follow setup wizard prompts
-2. Connect WiFi
-3. Add 15 sensors via discovery
-4. Configure 4 users
-5. Create 2 automation rules
-6. Arm system
-7. Receive first test alert</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1. Setup completed &lt;30 min
-2. all sensors recognized
-3. hub connected to WiFi
-4. mobile app functional
-5. Step completed as expected
-6. Step completed as expected
-7. Step completed as expected</t>
+          <t>Step 1: Follow setup wizard prompts
+Step 2: Connect WiFi
+Step 3: Add 15 sensors via discovery
+Step 4: Configure 4 users
+Step 5: Create 2 automation rules
+Step 6: Arm system
+Step 7: Receive first test alert</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Setup completed &lt;30 min
+Expected Outcome 2: all sensors recognized
+Expected Outcome 3: hub connected to WiFi
+Expected Outcome 4: mobile app functional
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>VAL-002</t>
+          <t>VAL-002: User Acceptance - Remote Arm/Disarm</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>User Acceptance - Remote Arm/Disarm</t>
+          <t>Verify user can arm/disarm from mobile app anywhere</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Verify user can arm/disarm from mobile app anywhere</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Resident away from home; receives alert; needs to disarm | Hub armed, mobile app installed, LTE connection available</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Resident away from home; receives alert; needs to disarm | Hub armed, mobile app installed, LTE connection available</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Arm system in away mode
-2. Leave home and verify armed status
-3. Trigger motion sensor (guest arriving)
-4. Receive alert on mobile app
-5. Tap 'Disarm' in app
-6. Verify alarm silences
-7. Check audit log</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1. Disarm successful &lt;5s
-2. alarm silenced
-3. notification sent
-4. audit log entry created
-5. Step completed as expected
-6. Verification successful
-7. Check completed</t>
+          <t>Step 1: Arm system in away mode
+Step 2: Leave home and verify armed status
+Step 3: Trigger motion sensor (guest arriving)
+Step 4: Receive alert on mobile app
+Step 5: Tap 'Disarm' in app
+Step 6: Verify alarm silences
+Step 7: Check audit log</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Disarm successful &lt;5s
+Expected Outcome 2: alarm silenced
+Expected Outcome 3: notification sent
+Expected Outcome 4: audit log entry created
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Verification successful
+Expected Outcome 7: Check completed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>VAL-003</t>
+          <t>VAL-003: User Acceptance - View Live Video</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>User Acceptance - View Live Video</t>
+          <t>Verify user can stream camera video on demand</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Verify user can stream camera video on demand</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Homeowner checking on property while away | Hub powered on, PoE camera recording, user on 4G LTE</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Homeowner checking on property while away | Hub powered on, PoE camera recording, user on 4G LTE</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Open mobile app
-2. Tap 'cameras' section
-3. Select front door camera
-4. Verify live video appears
-5. Observe quality (should be 720p on 4G)
-6. Switch to WiFi
-7. Verify quality improves to 4K
-8. Pause and resume stream</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1. Video streams in &lt;10s
-2. quality adapts to connection
-3. no buffering
-4. can pause/resume
-5. Step completed as expected
-6. Step completed as expected
-7. Verification successful
-8. Step completed as expected</t>
+          <t>Step 1: Open mobile app
+Step 2: Tap 'cameras' section
+Step 3: Select front door camera
+Step 4: Verify live video appears
+Step 5: Observe quality (should be 720p on 4G)
+Step 6: Switch to WiFi
+Step 7: Verify quality improves to 4K
+Step 8: Pause and resume stream</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Video streams in &lt;10s
+Expected Outcome 2: quality adapts to connection
+Expected Outcome 3: no buffering
+Expected Outcome 4: can pause/resume
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Verification successful
+Expected Outcome 8: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>VAL-004</t>
+          <t>VAL-004: User Acceptance - Event History</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>User Acceptance - Event History</t>
+          <t>Verify user can view 30 days of events</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Verify user can view 30 days of events</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Resident wants to review past incidents | Hub with 30 days events logged, mobile app</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Resident wants to review past incidents | Hub with 30 days events logged, mobile app</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Open app
-2. Navigate to event history
-3. Scroll through 30-day timeline
-4. Filter by motion events
-5. Filter by door openings
-6. Sort by most recent
-7. Tap event to see details</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1. Timeline displays all events
-2. filterable by type/sensor
-3. sortable by date
-4. &lt;5s load time
-5. Step completed as expected
-6. Step completed as expected
-7. Step completed as expected</t>
+          <t>Step 1: Open app
+Step 2: Navigate to event history
+Step 3: Scroll through 30-day timeline
+Step 4: Filter by motion events
+Step 5: Filter by door openings
+Step 6: Sort by most recent
+Step 7: Tap event to see details</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Timeline displays all events
+Expected Outcome 2: filterable by type/sensor
+Expected Outcome 3: sortable by date
+Expected Outcome 4: &lt;5s load time
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>VAL-005</t>
+          <t>VAL-005: User Acceptance - Automation Rules</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>User Acceptance - Automation Rules</t>
+          <t>Verify user can create conditional automation</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Verify user can create conditional automation</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Non-technical user wants: arm=lights off | Rules created visually; no code required; executed correctly; user sees confirmation</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Non-technical user wants: arm=lights off | Rules created visually; no code required; executed correctly; user sees confirmation</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Hub powered on, 10 Philips Hue lights configured, mobile app</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Step 1: Hub powered on, 10 Philips Hue lights configured, mobile app</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: P2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>VAL-006</t>
+          <t>VAL-006: User Acceptance - Settings Management</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>User Acceptance - Settings Management</t>
+          <t>Verify all settings accessible and changeable by admin</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Verify all settings accessible and changeable by admin</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Admin needs to change alert volume and notification preferences | Hub powered on, admin account, mobile app</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Admin needs to change alert volume and notification preferences | Hub powered on, admin account, mobile app</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as admin
-2. Open settings
-3. Change siren volume to 80dB
-4. Change notification preference to SMS only
-5. Add new user account
-6. Disable cloud upload
-7. Save all settings
-8. Reboot hub
-9. Verify settings persisted</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1. All settings persist after save
-2. changes apply immediately or on reboot as appropriate
-3. Step completed as expected
-4. Step completed as expected
-5. Step completed as expected
-6. Step completed as expected
-7. Step completed as expected
-8. Step completed as expected
-9. Verification successful</t>
+          <t>Step 1: Login as admin
+Step 2: Open settings
+Step 3: Change siren volume to 80dB
+Step 4: Change notification preference to SMS only
+Step 5: Add new user account
+Step 6: Disable cloud upload
+Step 7: Save all settings
+Step 8: Reboot hub
+Step 9: Verify settings persisted</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: All settings persist after save
+Expected Outcome 2: changes apply immediately or on reboot as appropriate
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Step completed as expected
+Expected Outcome 8: Step completed as expected
+Expected Outcome 9: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>VAL-007</t>
+          <t>VAL-007: Guest User Experience</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Guest User Experience</t>
+          <t>Verify guest user can view status only; cannot arm/disarm</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Verify guest user can view status only; cannot arm/disarm</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Family member visiting wants to check camera; not authorized to disarm | Hub powered on, guest account created, mobile app</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Family member visiting wants to check camera; not authorized to disarm | Hub powered on, guest account created, mobile app</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as guest
-2. Verify can view status
-3. Verify can view cameras
-4. Attempt to arm/disarm (should fail)
-5. Attempt to change settings (should fail)
-6. Verify view-only functions work</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1. Guest account restricted to view-only
-2. cannot change settings or disarm
-3. Verification successful
-4. Step completed as expected
-5. Step completed as expected
-6. Verification successful</t>
+          <t>Step 1: Login as guest
+Step 2: Verify can view status
+Step 3: Verify can view cameras
+Step 4: Attempt to arm/disarm (should fail)
+Step 5: Attempt to change settings (should fail)
+Step 6: Verify view-only functions work</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Guest account restricted to view-only
+Expected Outcome 2: cannot change settings or disarm
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>VAL-008</t>
+          <t>VAL-008: Technician Remote Support</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Technician Remote Support</t>
+          <t>Verify technician can diagnose issues without full access</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Verify technician can diagnose issues without full access</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Support technician needs to view hub logs for troubleshooting | Hub powered on, technician account created, issue logged</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Support technician needs to view hub logs for troubleshooting | Hub powered on, technician account created, issue logged</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1. Technician login with limited role
-2. View system logs
-3. View sensor status
-4. Attempt to disarm (should fail)
-5. Attempt to modify settings (should fail)
-6. Verify can collect diagnostic data</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1. Technician sees logs and system state
-2. cannot modify settings or view video
-3. Step completed as expected
-4. Step completed as expected
-5. Step completed as expected
-6. Verification successful</t>
+          <t>Step 1: Technician login with limited role
+Step 2: View system logs
+Step 3: View sensor status
+Step 4: Attempt to disarm (should fail)
+Step 5: Attempt to modify settings (should fail)
+Step 6: Verify can collect diagnostic data</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Technician sees logs and system state
+Expected Outcome 2: cannot modify settings or view video
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>VAL-009</t>
+          <t>VAL-009: Load Test - 20 Concurrent Events</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Load Test - 20 Concurrent Events</t>
+          <t>Verify hub processes 20 simultaneous sensor triggers without data loss</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Verify hub processes 20 simultaneous sensor triggers without data loss</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Multiple sensors triggered simultaneously (e.g. | All 20 events logged; none lost; latency &lt;5s for last event; system remains responsive</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Multiple sensors triggered simultaneously (e.g. | All 20 events logged; none lost; latency &lt;5s for last event; system remains responsive</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Hub powered on, 20+ sensors configured, event injection script ready</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Step 1: Hub powered on, 20+ sensors configured, event injection script ready</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: P0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>VAL-010</t>
+          <t>VAL-010: Load Test - 100 Events in 1 Hour</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Load Test - 100 Events in 1 Hour</t>
+          <t>Verify hub maintains performance under sustained load</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Verify hub maintains performance under sustained load</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Active home with frequent motion detection | All 100 events logged; latency remains &lt;1s average; system responsive; no crashes</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Active home with frequent motion detection | All 100 events logged; latency remains &lt;1s average; system responsive; no crashes</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Hub powered on, events logged continuously for 1 hour</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Step 1: Hub powered on, events logged continuously for 1 hour</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: P1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>VAL-011</t>
+          <t>VAL-011: Stress Test - WiFi Connectivity Loss</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Stress Test - WiFi Connectivity Loss</t>
+          <t>Verify system survives 10 WiFi disconnections in sequence</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Verify system survives 10 WiFi disconnections in sequence</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>WiFi router power cycles or interference causes drops | Hub with WiFi and cellular, sensors active, event injection</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>WiFi router power cycles or interference causes drops | Hub with WiFi and cellular, sensors active, event injection</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1. Establish WiFi connection
-2. Disconnect WiFi (power off router)
-3. Wait for cellular failover
-4. Send test event via sensor
-5. Verify event received via cellular
-6. Reconnect WiFi (power on router)
-7. Verify hub switches back to WiFi
-8. Repeat 10 times
-9. Verify no event loss</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1. Each disconnection triggers failover
-2. no alert loss
-3. system recovers without intervention
-4. Step completed as expected
-5. Verification successful
-6. Step completed as expected
-7. Verification successful
-8. Step completed as expected
-9. Verification successful</t>
+          <t>Step 1: Establish WiFi connection
+Step 2: Disconnect WiFi (power off router)
+Step 3: Wait for cellular failover
+Step 4: Send test event via sensor
+Step 5: Verify event received via cellular
+Step 6: Reconnect WiFi (power on router)
+Step 7: Verify hub switches back to WiFi
+Step 8: Repeat 10 times
+Step 9: Verify no event loss</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Each disconnection triggers failover
+Expected Outcome 2: no alert loss
+Expected Outcome 3: system recovers without intervention
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Verification successful
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Verification successful
+Expected Outcome 8: Step completed as expected
+Expected Outcome 9: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>VAL-012</t>
+          <t>VAL-012: Stress Test - LoRaWAN Mesh Resilience</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Stress Test - LoRaWAN Mesh Resilience</t>
+          <t>Verify mesh network recovers from node failures</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Verify mesh network recovers from node failures</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Sensor battery dies; mesh must reroute around dead node | Hub with LoRaWAN, 5 mesh-capable sensors, power control for each</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Sensor battery dies; mesh must reroute around dead node | Hub with LoRaWAN, 5 mesh-capable sensors, power control for each</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1. Enable LoRaWAN mesh
-2. Trigger events (all sensors responsive)
-3. Power off middle sensor (node 3 of 5)
-4. Trigger events again
-5. Verify events still delivered via alternate path
-6. Power on sensor 3
-7. Verify mesh re-forms</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1. Mesh network remains connected
-2. reroutes around failed node
-3. events still delivered
-4. Action triggered successfully
-5. Verification successful
-6. Step completed as expected
-7. Verification successful</t>
+          <t>Step 1: Enable LoRaWAN mesh
+Step 2: Trigger events (all sensors responsive)
+Step 3: Power off middle sensor (node 3 of 5)
+Step 4: Trigger events again
+Step 5: Verify events still delivered via alternate path
+Step 6: Power on sensor 3
+Step 7: Verify mesh re-forms</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Mesh network remains connected
+Expected Outcome 2: reroutes around failed node
+Expected Outcome 3: events still delivered
+Expected Outcome 4: Action triggered successfully
+Expected Outcome 5: Verification successful
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>VAL-013</t>
+          <t>VAL-013: Stress Test - Video Recording During Event</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Stress Test - Video Recording During Event</t>
+          <t>Verify video continues recording during high-activity period</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Verify video continues recording during high-activity period</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Intrusion in progress; multiple sensors trigger; video must not drop frames | Hub powered on, PoE camera recording, event injection scenario</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Intrusion in progress; multiple sensors trigger; video must not drop frames | Hub powered on, PoE camera recording, event injection scenario</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1. Start continuous video recording
-2. Trigger 20 sensors in rapid sequence
-3. Monitor video timeline
-4. Verify no dropped frames
-5. Verify no gaps in recording
-6. Check hub CPU usage
-7. Verify video stored successfully</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1. Video recording uninterrupted
-2. frame rate maintained
-3. no gaps in timeline
-4. full event captured
-5. Verification successful
-6. Check completed
-7. Verification successful</t>
+          <t>Step 1: Start continuous video recording
+Step 2: Trigger 20 sensors in rapid sequence
+Step 3: Monitor video timeline
+Step 4: Verify no dropped frames
+Step 5: Verify no gaps in recording
+Step 6: Check hub CPU usage
+Step 7: Verify video stored successfully</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Video recording uninterrupted
+Expected Outcome 2: frame rate maintained
+Expected Outcome 3: no gaps in timeline
+Expected Outcome 4: full event captured
+Expected Outcome 5: Verification successful
+Expected Outcome 6: Check completed
+Expected Outcome 7: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>VAL-014</t>
+          <t>VAL-014: Stress Test - Cloud Unavailability</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Stress Test - Cloud Unavailability</t>
+          <t>Verify local operation continues during cloud outage</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Verify local operation continues during cloud outage</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>AWS IoT Hub offline for maintenance (typical 15 min SLA) | Hub configured for hybrid operation, cloud service available initially</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>AWS IoT Hub offline for maintenance (typical 15 min SLA) | Hub configured for hybrid operation, cloud service available initially</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1. Enable cloud sync
-2. Verify initial cloud connection
-3. Disable cloud connectivity (firewall block)
-4. Trigger sensors continuously for 30 min
-5. Log all events locally
-6. Re-enable cloud connectivity
-7. Verify sync completes
-8. Verify no event loss</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1. Local monitoring continues unaffected
-2. events logged
-3. no alert loss
-4. sync resumes when cloud returns
-5. Step completed as expected
-6. Step completed as expected
-7. Verification successful
-8. Verification successful</t>
+          <t>Step 1: Enable cloud sync
+Step 2: Verify initial cloud connection
+Step 3: Disable cloud connectivity (firewall block)
+Step 4: Trigger sensors continuously for 30 min
+Step 5: Log all events locally
+Step 6: Re-enable cloud connectivity
+Step 7: Verify sync completes
+Step 8: Verify no event loss</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Local monitoring continues unaffected
+Expected Outcome 2: events logged
+Expected Outcome 3: no alert loss
+Expected Outcome 4: sync resumes when cloud returns
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Verification successful
+Expected Outcome 8: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>VAL-015</t>
+          <t>VAL-015: Failover Chain - WiFi to Cellular to Mesh</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Failover Chain - WiFi to Cellular to Mesh</t>
+          <t>Verify automatic cascade through all connectivity options</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Verify automatic cascade through all connectivity options</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>WiFi down | P1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>WiFi down | P1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Each failover triggers automatically; &lt;30s total; no alert loss; system uses best available path</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> mesh available</t>
+          <t>Step 1: Each failover triggers automatically; &lt;30s total; no alert loss; system uses best available path</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: mesh available</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>VAL-016</t>
+          <t>VAL-016: Resilience - Hub Battery Backup Duration</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Resilience - Hub Battery Backup Duration</t>
+          <t>Verify 4+ hour battery backup during power outage</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Verify 4+ hour battery backup during power outage</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Extended power outage (common in storms) | Hub with UPS battery, power removal scenario</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Extended power outage (common in storms) | Hub with UPS battery, power removal scenario</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1. Power on hub and UPS battery
-2. Verify fully charged (~4000 mAh)
-3. Turn off main power
-4. Monitor hub operation
-5. Track battery voltage/time
-6. Continue monitoring until shutdown
-7. Verify UPS provides power
-8. Record total operation time</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1. System operates on battery for 4+ hours
-2. all functions maintained
-3. graceful shutdown if outage longer
-4. Step completed as expected
-5. Step completed as expected
-6. Step completed as expected
-7. Verification successful
-8. Step completed as expected</t>
+          <t>Step 1: Power on hub and UPS battery
+Step 2: Verify fully charged (~4000 mAh)
+Step 3: Turn off main power
+Step 4: Monitor hub operation
+Step 5: Track battery voltage/time
+Step 6: Continue monitoring until shutdown
+Step 7: Verify UPS provides power
+Step 8: Record total operation time</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: System operates on battery for 4+ hours
+Expected Outcome 2: all functions maintained
+Expected Outcome 3: graceful shutdown if outage longer
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Verification successful
+Expected Outcome 8: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>VAL-017</t>
+          <t>VAL-017: Resilience - Off-Grid Operation</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Resilience - Off-Grid Operation</t>
+          <t>Verify complete autonomy without internet/power backup</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Verify complete autonomy without internet/power backup</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Remote mountain cabin with no ISP/cellular coverage; local operation only | Hub with LoRaWAN only (WiFi/cellular disabled), 15 sensors, solar power (simulated)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Remote mountain cabin with no ISP/cellular coverage; local operation only | Hub with LoRaWAN only (WiFi/cellular disabled), 15 sensors, solar power (simulated)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1. Disable all connectivity except LoRaWAN
-2. Power hub via solar simulation
-3. Deploy sensors in test environment
-4. Trigger motion/door/water events
-5. Monitor hub event log
-6. Arm and disarm system via local button
-7. Verify video recording continues
-8. Run for 24 hours</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1. System operates independently
-2. all monitoring functions active
-3. events logged locally
-4. no cloud dependency
-5. Step completed as expected
-6. Step completed as expected
-7. Verification successful
-8. Step completed as expected</t>
+          <t>Step 1: Disable all connectivity except LoRaWAN
+Step 2: Power hub via solar simulation
+Step 3: Deploy sensors in test environment
+Step 4: Trigger motion/door/water events
+Step 5: Monitor hub event log
+Step 6: Arm and disarm system via local button
+Step 7: Verify video recording continues
+Step 8: Run for 24 hours</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: System operates independently
+Expected Outcome 2: all monitoring functions active
+Expected Outcome 3: events logged locally
+Expected Outcome 4: no cloud dependency
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Verification successful
+Expected Outcome 8: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>VAL-018</t>
+          <t>VAL-018: Resilience - Failover to Satellite (Future)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Resilience - Failover to Satellite (Future)</t>
+          <t>Verify satellite connectivity option for extreme off-grid</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Verify satellite connectivity option for extreme off-grid</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Ultra-remote property with no terrestrial coverage | Hub with optional satellite modem, Starlink service</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Ultra-remote property with no terrestrial coverage | Hub with optional satellite modem, Starlink service</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1. Configure satellite modem
-2. Establish satellite link
-3. Queue 10 events locally
-4. Send sync command
-5. Verify events upload to cloud
-6. Receive alert via satellite (latency 600-1000ms acceptable)</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1. Satellite link establishes
-2. events sync
-3. alert delivery works (high latency OK)
-4. Step completed as expected
-5. Verification successful
-6. Step completed as expected</t>
+          <t>Step 1: Configure satellite modem
+Step 2: Establish satellite link
+Step 3: Queue 10 events locally
+Step 4: Send sync command
+Step 5: Verify events upload to cloud
+Step 6: Receive alert via satellite (latency 600-1000ms acceptable)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Satellite link establishes
+Expected Outcome 2: events sync
+Expected Outcome 3: alert delivery works (high latency OK)
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Verification successful
+Expected Outcome 6: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>VAL-019</t>
+          <t>VAL-019: Compliance - GDPR Data Export</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Compliance - GDPR Data Export</t>
+          <t>Verify user can export all personal data in standard format</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Verify user can export all personal data in standard format</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>EU resident requests data under GDPR right to access | Hub powered on, 30 days of events logged, user requests export</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>EU resident requests data under GDPR right to access | Hub powered on, 30 days of events logged, user requests export</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as user
-2. Navigate to data export
-3. Request complete data export
-4. Receive download link within 7 days
-5. Download JSON file
-6. Verify completeness (events, settings, users, metadata)</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1. All user data exported as JSON
-2. includes events, settings, user accounts, video metadata (not video files)
-3. &lt;7 days
-4. Step completed as expected
-5. Step completed as expected
-6. Verification successful</t>
+          <t>Step 1: Login as user
+Step 2: Navigate to data export
+Step 3: Request complete data export
+Step 4: Receive download link within 7 days
+Step 5: Download JSON file
+Step 6: Verify completeness (events, settings, users, metadata)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: All user data exported as JSON
+Expected Outcome 2: includes events, settings, user accounts, video metadata (not video files)
+Expected Outcome 3: &lt;7 days
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>VAL-020</t>
+          <t>VAL-020: Compliance - Data Deletion</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Compliance - Data Deletion</t>
+          <t>Verify user can delete account and associated data</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Verify user can delete account and associated data</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>User opts to remove system; requests data deletion | Hub powered on, user account with 30 days events</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>User opts to remove system; requests data deletion | Hub powered on, user account with 30 days events</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as user
-2. Request account deletion
-3. Confirm deletion request
-4. Data retained for 30-day recovery period
-5. After 30 days, verify deletion complete
-6. Verify user cannot login
-7. Verify audit trail retained (no personal data)</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1. Account deleted
-2. personal data removed except audit trail
-3. 30-day recovery period offered
-4. Step completed as expected
-5. Verification successful
-6. Verification successful
-7. Verification successful</t>
+          <t>Step 1: Login as user
+Step 2: Request account deletion
+Step 3: Confirm deletion request
+Step 4: Data retained for 30-day recovery period
+Step 5: After 30 days, verify deletion complete
+Step 6: Verify user cannot login
+Step 7: Verify audit trail retained (no personal data)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Account deleted
+Expected Outcome 2: personal data removed except audit trail
+Expected Outcome 3: 30-day recovery period offered
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Verification successful
+Expected Outcome 6: Verification successful
+Expected Outcome 7: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>VAL-021</t>
+          <t>VAL-021: Regulatory - FCC Certification</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Regulatory - FCC Certification</t>
+          <t>Verify RF emissions within FCC limits</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Verify RF emissions within FCC limits</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>System operates within RF spectrum regulations | Hub with all transmitters, test chamber (external validation)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>System operates within RF spectrum regulations | Hub with all transmitters, test chamber (external validation)</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1. Test WiFi emissions (2.4GHz, 5GHz)
-2. Test LoRaWAN emissions (915MHz)
-3. Test LTE modem emissions
-4. Compare to FCC Part 15 limits
-5. Document compliance
-6. Obtain FCC certification</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1. LoRaWAN/WiFi/LTE emissions meet FCC Part 15
-2. certification documentation available
-3. Step completed as expected
-4. Step completed as expected
-5. Step completed as expected
-6. Step completed as expected</t>
+          <t>Step 1: Test WiFi emissions (2.4GHz, 5GHz)
+Step 2: Test LoRaWAN emissions (915MHz)
+Step 3: Test LTE modem emissions
+Step 4: Compare to FCC Part 15 limits
+Step 5: Document compliance
+Step 6: Obtain FCC certification</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: LoRaWAN/WiFi/LTE emissions meet FCC Part 15
+Expected Outcome 2: certification documentation available
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>VAL-022</t>
+          <t>VAL-022: Performance - Sub-1s Motion Alert Latency</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Performance - Sub-1s Motion Alert Latency</t>
+          <t>Verify motion detection to alert delivery &lt;1s end-to-end</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Verify motion detection to alert delivery &lt;1s end-to-end</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Motion triggers alert on user phone in &lt;1 second | Hub powered on, motion sensor, mobile app, WiFi/cellular active</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Motion triggers alert on user phone in &lt;1 second | Hub powered on, motion sensor, mobile app, WiFi/cellular active</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1. Arm system
-2. Position phone and sensor
-3. Trigger motion sensor (precise time)
-4. Measure app notification time
-5. Calculate e2e latency
-6. Repeat 10 times
-7. Average results</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1. Latency from motion sensor trigger to notification received: &lt;1000ms on WiFi, &lt;2000ms on cellular
-2. Step completed as expected
-3. Action triggered successfully
-4. Step completed as expected
-5. Step completed as expected
-6. Step completed as expected
-7. Step completed as expected</t>
+          <t>Step 1: Arm system
+Step 2: Position phone and sensor
+Step 3: Trigger motion sensor (precise time)
+Step 4: Measure app notification time
+Step 5: Calculate e2e latency
+Step 6: Repeat 10 times
+Step 7: Average results</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Latency from motion sensor trigger to notification received: &lt;1000ms on WiFi, &lt;2000ms on cellular
+Expected Outcome 2: Step completed as expected
+Expected Outcome 3: Action triggered successfully
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>VAL-023</t>
+          <t>VAL-023: Performance - 30-Frame Video Capture</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Performance - 30-Frame Video Capture</t>
+          <t>Verify video sustained at 30fps without drops</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Verify video sustained at 30fps without drops</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Video quality maintained during normal operation | Hub powered on, PoE camera, continuous operation 4 hours</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Video quality maintained during normal operation | Hub powered on, PoE camera, continuous operation 4 hours</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>1. Start 24/7 recording mode
-2. Record for 4 hours continuously
-3. Capture frame rate every 30 seconds
-4. Count dropped frames
-5. Check file integrity
-6. Verify storage usage</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>1. 4K video recorded at consistent 30fps
-2. &lt;5 dropped frames per hour
-3. file integrity verified
-4. Step completed as expected
-5. Check completed
-6. Verification successful</t>
+          <t>Step 1: Start 24/7 recording mode
+Step 2: Record for 4 hours continuously
+Step 3: Capture frame rate every 30 seconds
+Step 4: Count dropped frames
+Step 5: Check file integrity
+Step 6: Verify storage usage</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: 4K video recorded at consistent 30fps
+Expected Outcome 2: &lt;5 dropped frames per hour
+Expected Outcome 3: file integrity verified
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Check completed
+Expected Outcome 6: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>VAL-024</t>
+          <t>VAL-024: Performance - Sub-5s Command Response</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Performance - Sub-5s Command Response</t>
+          <t>Verify lock/light commands execute within 5 seconds</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Verify lock/light commands execute within 5 seconds</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>User sends unlock command; door unlocks promptly | Hub powered on, WiFi smart lock and lights, mobile app</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>User sends unlock command; door unlocks promptly | Hub powered on, WiFi smart lock and lights, mobile app</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1. Send lock command via app
-2. Measure lock servo response
-3. Send light command
-4. Measure light response
-5. Repeat 20 times for each command
-6. Calculate average and max latency</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1. Command sent to device
-2. state change confirmed: &lt;5 seconds average, &lt;10 seconds max
-3. Step completed as expected
-4. Step completed as expected
-5. Step completed as expected
-6. Step completed as expected</t>
+          <t>Step 1: Send lock command via app
+Step 2: Measure lock servo response
+Step 3: Send light command
+Step 4: Measure light response
+Step 5: Repeat 20 times for each command
+Step 6: Calculate average and max latency</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Command sent to device
+Expected Outcome 2: state change confirmed: &lt;5 seconds average, &lt;10 seconds max
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>VAL-025</t>
+          <t>VAL-025: User Satisfaction - Setup Simplicity</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>User Satisfaction - Setup Simplicity</t>
+          <t>Verify non-technical user can deploy without professional help</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Verify non-technical user can deploy without professional help</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>New user from target demographic attempts setup alone | Setup kit, blank hub, 15 sensors, non-technical user (representative demographic)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>New user from target demographic attempts setup alone | Setup kit, blank hub, 15 sensors, non-technical user (representative demographic)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1. Provide user with setup kit and instructions
-2. User follows setup wizard without assistance
-3. Observe process
-4. Time to completion
-5. Note any confusion points
-6. Post-setup survey on ease/confidence</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1. User completes setup without external help
-2. confidence rating &gt;8/10
-3. no frustration evident
-4. Step completed as expected
-5. Step completed as expected
-6. Step completed as expected</t>
+          <t>Step 1: Provide user with setup kit and instructions
+Step 2: User follows setup wizard without assistance
+Step 3: Observe process
+Step 4: Time to completion
+Step 5: Note any confusion points
+Step 6: Post-setup survey on ease/confidence</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: User completes setup without external help
+Expected Outcome 2: confidence rating &gt;8/10
+Expected Outcome 3: no frustration evident
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>VAL-026</t>
+          <t>VAL-026: Cost-Effectiveness - ROI Analysis</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Cost-Effectiveness - ROI Analysis</t>
+          <t>Verify system cost-effective vs professional alternatives</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Verify system cost-effective vs professional alternatives</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Compare DIY system vs monthly security service | N/A - financial analysis</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Compare DIY system vs monthly security service | N/A - financial analysis</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1. Calculate system TCO: hardware $4,335 + 5-year service ($600)
-2. Calculate professional TCO: $2,500 install + $40/month * 60 = $4,900
-3. Compare
-4. Calculate payback period</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1. Hardware cost $4,335 + $120/year &lt; professional service $2,500 install + $40/month
-2. Step completed as expected
-3. Step completed as expected
-4. Step completed as expected</t>
+          <t>Step 1: Calculate system TCO: hardware $4,335 + 5-year service ($600)
+Step 2: Calculate professional TCO: $2,500 install + $40/month * 60 = $4,900
+Step 3: Compare
+Step 4: Calculate payback period</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Hardware cost $4,335 + $120/year &lt; professional service $2,500 install + $40/month
+Expected Outcome 2: Step completed as expected
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Step completed as expected</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>VAL-027</t>
+          <t>VAL-027: Interoperability - Multi-Vendor Support</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Interoperability - Multi-Vendor Support</t>
+          <t>Verify system works with existing smart home devices</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Verify system works with existing smart home devices</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Homeowner has existing WiFi smart lights and locks | Hub powered on, existing smart devices (Hue, Wemo, Nuki, LIFX, etc.)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Homeowner has existing WiFi smart lights and locks | Hub powered on, existing smart devices (Hue, Wemo, Nuki, LIFX, etc.)</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>1. Add existing Hue lights to hub
-2. Control via hub app
-3. Add existing Wemo outlet
-4. Control via hub app
-5. Add existing Nuki lock
-6. Lock/unlock via hub
-7. Verify automation rules work with all devices</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>1. System integrates with standard WiFi/Zigbee devices
-2. no proprietary lock-in
-3. easy add/remove
-4. Step completed as expected
-5. Step completed as expected
-6. Step completed as expected
-7. Verification successful</t>
+          <t>Step 1: Add existing Hue lights to hub
+Step 2: Control via hub app
+Step 3: Add existing Wemo outlet
+Step 4: Control via hub app
+Step 5: Add existing Nuki lock
+Step 6: Lock/unlock via hub
+Step 7: Verify automation rules work with all devices</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: System integrates with standard WiFi/Zigbee devices
+Expected Outcome 2: no proprietary lock-in
+Expected Outcome 3: easy add/remove
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Step completed as expected
+Expected Outcome 7: Verification successful</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>VAL-028</t>
+          <t>VAL-028: Extensibility - Future Device Addition</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Extensibility - Future Device Addition</t>
+          <t>Verify user can add new devices without hub replacement</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Verify user can add new devices without hub replacement</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>User wants to add 2 new cameras next year | Hub powered on, 20 devices deployed</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>User wants to add 2 new cameras next year | Hub powered on, 20 devices deployed</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1. Add 20th, 30th, 40th device
-2. Monitor hub performance
-3. Verify no degradation
-4. Check firmware update process
-5. Deploy new device type via firmware update</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1. Hub supports 50+ devices without degradation
-2. firmware update adds new device support
-3. Verification successful
-4. Check completed
-5. Step completed as expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+          <t>Step 1: Add 20th, 30th, 40th device
+Step 2: Monitor hub performance
+Step 3: Verify no degradation
+Step 4: Check firmware update process
+Step 5: Deploy new device type via firmware update</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Hub supports 50+ devices without degradation
+Expected Outcome 2: firmware update adds new device support
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Check completed
+Expected Outcome 5: Step completed as expected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
